--- a/output/campaigns/US-GF-20260707-001/Prospect_List.xlsx
+++ b/output/campaigns/US-GF-20260707-001/Prospect_List.xlsx
@@ -170,7 +170,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
